--- a/Output/Questionnaires_combined.xlsx
+++ b/Output/Questionnaires_combined.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:ES138"/>
+  <dimension ref="A1:ET138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="24" max="24" width="20.7109375" style="2" customWidth="1"/>
@@ -1102,10 +1102,15 @@
       </c>
       <c r="ER1" s="1" t="inlineStr">
         <is>
+          <t>vas_fatigue</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
           <t>qslaq_score</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>qslaq_symptom_score</t>
         </is>
@@ -1538,9 +1543,12 @@
         </is>
       </c>
       <c r="ER2">
+        <v>30</v>
+      </c>
+      <c r="ES2">
         <v>11</v>
       </c>
-      <c r="ES2">
+      <c r="ET2">
         <v>11</v>
       </c>
     </row>
@@ -1966,9 +1974,12 @@
         </is>
       </c>
       <c r="ER3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="ES3">
+        <v>5</v>
+      </c>
+      <c r="ET3">
         <v>3</v>
       </c>
     </row>
@@ -2399,9 +2410,12 @@
         </is>
       </c>
       <c r="ER4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="ES4">
+        <v>1</v>
+      </c>
+      <c r="ET4">
         <v>1</v>
       </c>
     </row>
@@ -2848,9 +2862,12 @@
         </is>
       </c>
       <c r="ER5">
+        <v>70</v>
+      </c>
+      <c r="ES5">
         <v>6</v>
       </c>
-      <c r="ES5">
+      <c r="ET5">
         <v>5</v>
       </c>
     </row>
@@ -3297,9 +3314,12 @@
         </is>
       </c>
       <c r="ER6">
+        <v>70</v>
+      </c>
+      <c r="ES6">
         <v>10</v>
       </c>
-      <c r="ES6">
+      <c r="ET6">
         <v>8</v>
       </c>
     </row>
@@ -3725,9 +3745,12 @@
         </is>
       </c>
       <c r="ER7">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="ES7">
+        <v>4</v>
+      </c>
+      <c r="ET7">
         <v>4</v>
       </c>
     </row>
@@ -4153,9 +4176,12 @@
         </is>
       </c>
       <c r="ER8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="ES8">
+        <v>5</v>
+      </c>
+      <c r="ET8">
         <v>5</v>
       </c>
     </row>
@@ -4607,9 +4633,12 @@
         </is>
       </c>
       <c r="ER9">
+        <v>60</v>
+      </c>
+      <c r="ES9">
         <v>7</v>
       </c>
-      <c r="ES9">
+      <c r="ET9">
         <v>9</v>
       </c>
     </row>
@@ -5056,9 +5085,12 @@
         </is>
       </c>
       <c r="ER10">
+        <v>80</v>
+      </c>
+      <c r="ES10">
         <v>8</v>
       </c>
-      <c r="ES10">
+      <c r="ET10">
         <v>9</v>
       </c>
     </row>
@@ -5394,9 +5426,12 @@
         </is>
       </c>
       <c r="ER11">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="ES11">
+        <v>5</v>
+      </c>
+      <c r="ET11">
         <v>4</v>
       </c>
     </row>
@@ -5732,9 +5767,12 @@
         </is>
       </c>
       <c r="ER12">
+        <v>70</v>
+      </c>
+      <c r="ES12">
         <v>6</v>
       </c>
-      <c r="ES12">
+      <c r="ET12">
         <v>5</v>
       </c>
     </row>
@@ -6178,9 +6216,12 @@
         </is>
       </c>
       <c r="ER13">
+        <v>60</v>
+      </c>
+      <c r="ES13">
         <v>19</v>
       </c>
-      <c r="ES13">
+      <c r="ET13">
         <v>12</v>
       </c>
     </row>
@@ -6624,9 +6665,12 @@
         </is>
       </c>
       <c r="ER14">
+        <v>80</v>
+      </c>
+      <c r="ES14">
         <v>16</v>
       </c>
-      <c r="ES14">
+      <c r="ET14">
         <v>12</v>
       </c>
     </row>
@@ -7052,9 +7096,12 @@
         </is>
       </c>
       <c r="ER15">
+        <v>30</v>
+      </c>
+      <c r="ES15">
         <v>8</v>
       </c>
-      <c r="ES15">
+      <c r="ET15">
         <v>10</v>
       </c>
     </row>
@@ -7480,9 +7527,12 @@
         </is>
       </c>
       <c r="ER16">
+        <v>20</v>
+      </c>
+      <c r="ES16">
         <v>13</v>
       </c>
-      <c r="ES16">
+      <c r="ET16">
         <v>12</v>
       </c>
     </row>
@@ -7929,9 +7979,12 @@
         </is>
       </c>
       <c r="ER17">
+        <v>70</v>
+      </c>
+      <c r="ES17">
         <v>18</v>
       </c>
-      <c r="ES17">
+      <c r="ET17">
         <v>12</v>
       </c>
     </row>
@@ -8383,9 +8436,12 @@
         </is>
       </c>
       <c r="ER18">
+        <v>70</v>
+      </c>
+      <c r="ES18">
         <v>17</v>
       </c>
-      <c r="ES18">
+      <c r="ET18">
         <v>12</v>
       </c>
     </row>
@@ -8811,9 +8867,12 @@
         </is>
       </c>
       <c r="ER19">
+        <v>30</v>
+      </c>
+      <c r="ES19">
         <v>11</v>
       </c>
-      <c r="ES19">
+      <c r="ET19">
         <v>8</v>
       </c>
     </row>
@@ -9265,9 +9324,12 @@
         </is>
       </c>
       <c r="ER20">
+        <v>50</v>
+      </c>
+      <c r="ES20">
         <v>19</v>
       </c>
-      <c r="ES20">
+      <c r="ET20">
         <v>16</v>
       </c>
     </row>
@@ -9714,9 +9776,12 @@
         </is>
       </c>
       <c r="ER21">
+        <v>50</v>
+      </c>
+      <c r="ES21">
         <v>10</v>
       </c>
-      <c r="ES21">
+      <c r="ET21">
         <v>9</v>
       </c>
     </row>
@@ -10168,9 +10233,12 @@
         </is>
       </c>
       <c r="ER22">
+        <v>40</v>
+      </c>
+      <c r="ES22">
         <v>15</v>
       </c>
-      <c r="ES22">
+      <c r="ET22">
         <v>13</v>
       </c>
     </row>
@@ -10617,9 +10685,12 @@
         </is>
       </c>
       <c r="ER23">
+        <v>70</v>
+      </c>
+      <c r="ES23">
         <v>10</v>
       </c>
-      <c r="ES23">
+      <c r="ET23">
         <v>7</v>
       </c>
     </row>
@@ -11066,9 +11137,12 @@
         </is>
       </c>
       <c r="ER24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ES24">
+        <v>0</v>
+      </c>
+      <c r="ET24">
         <v>0</v>
       </c>
     </row>
@@ -11520,6 +11594,9 @@
       <c r="ES25">
         <v>0</v>
       </c>
+      <c r="ET25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11964,9 +12041,12 @@
         </is>
       </c>
       <c r="ER26">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="ES26">
+        <v>3</v>
+      </c>
+      <c r="ET26">
         <v>3</v>
       </c>
     </row>
@@ -12413,9 +12493,12 @@
         </is>
       </c>
       <c r="ER27">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="ES27">
+        <v>3</v>
+      </c>
+      <c r="ET27">
         <v>3</v>
       </c>
     </row>
@@ -12841,9 +12924,12 @@
         </is>
       </c>
       <c r="ER28">
+        <v>40</v>
+      </c>
+      <c r="ES28">
         <v>6</v>
       </c>
-      <c r="ES28">
+      <c r="ET28">
         <v>6</v>
       </c>
     </row>
@@ -13269,9 +13355,12 @@
         </is>
       </c>
       <c r="ER29">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="ES29">
+        <v>3</v>
+      </c>
+      <c r="ET29">
         <v>2</v>
       </c>
     </row>
@@ -13697,9 +13786,12 @@
         </is>
       </c>
       <c r="ER30">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="ES30">
+        <v>3</v>
+      </c>
+      <c r="ET30">
         <v>3</v>
       </c>
     </row>
@@ -14125,9 +14217,12 @@
         </is>
       </c>
       <c r="ER31">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="ES31">
+        <v>2</v>
+      </c>
+      <c r="ET31">
         <v>2</v>
       </c>
     </row>
@@ -14553,9 +14648,12 @@
         </is>
       </c>
       <c r="ER32">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="ES32">
+        <v>1</v>
+      </c>
+      <c r="ET32">
         <v>1</v>
       </c>
     </row>
@@ -14981,9 +15079,12 @@
         </is>
       </c>
       <c r="ER33">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="ES33">
+        <v>1</v>
+      </c>
+      <c r="ET33">
         <v>1</v>
       </c>
     </row>
@@ -15409,9 +15510,12 @@
         </is>
       </c>
       <c r="ER34">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="ES34">
+        <v>1</v>
+      </c>
+      <c r="ET34">
         <v>1</v>
       </c>
     </row>
@@ -15837,9 +15941,12 @@
         </is>
       </c>
       <c r="ER35">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="ES35">
+        <v>1</v>
+      </c>
+      <c r="ET35">
         <v>1</v>
       </c>
     </row>
@@ -16286,9 +16393,12 @@
         </is>
       </c>
       <c r="ER36">
+        <v>30</v>
+      </c>
+      <c r="ES36">
         <v>8</v>
       </c>
-      <c r="ES36">
+      <c r="ET36">
         <v>9</v>
       </c>
     </row>
@@ -16735,9 +16845,12 @@
         </is>
       </c>
       <c r="ER37">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="ES37">
+        <v>4</v>
+      </c>
+      <c r="ET37">
         <v>6</v>
       </c>
     </row>
@@ -17157,9 +17270,12 @@
         </is>
       </c>
       <c r="ER38">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="ES38">
+        <v>4</v>
+      </c>
+      <c r="ET38">
         <v>4</v>
       </c>
     </row>
@@ -17590,9 +17706,12 @@
         </is>
       </c>
       <c r="ER39">
+        <v>60</v>
+      </c>
+      <c r="ES39">
         <v>6</v>
       </c>
-      <c r="ES39">
+      <c r="ET39">
         <v>7</v>
       </c>
     </row>
@@ -18018,9 +18137,12 @@
         </is>
       </c>
       <c r="ER40">
+        <v>65</v>
+      </c>
+      <c r="ES40">
         <v>12</v>
       </c>
-      <c r="ES40">
+      <c r="ET40">
         <v>13</v>
       </c>
     </row>
@@ -18446,9 +18568,12 @@
         </is>
       </c>
       <c r="ER41">
+        <v>87</v>
+      </c>
+      <c r="ES41">
         <v>13</v>
       </c>
-      <c r="ES41">
+      <c r="ET41">
         <v>12</v>
       </c>
     </row>
@@ -18900,9 +19025,12 @@
         </is>
       </c>
       <c r="ER42">
+        <v>70</v>
+      </c>
+      <c r="ES42">
         <v>17</v>
       </c>
-      <c r="ES42">
+      <c r="ET42">
         <v>11</v>
       </c>
     </row>
@@ -19349,9 +19477,12 @@
         </is>
       </c>
       <c r="ER43">
+        <v>70</v>
+      </c>
+      <c r="ES43">
         <v>14</v>
       </c>
-      <c r="ES43">
+      <c r="ET43">
         <v>10</v>
       </c>
     </row>
@@ -19797,9 +19928,12 @@
         </is>
       </c>
       <c r="ER44">
+        <v>70</v>
+      </c>
+      <c r="ES44">
         <v>9</v>
       </c>
-      <c r="ES44">
+      <c r="ET44">
         <v>13</v>
       </c>
     </row>
@@ -20248,9 +20382,12 @@
         </is>
       </c>
       <c r="ER45">
+        <v>30</v>
+      </c>
+      <c r="ES45">
         <v>6</v>
       </c>
-      <c r="ES45">
+      <c r="ET45">
         <v>7</v>
       </c>
     </row>
@@ -20681,9 +20818,12 @@
         </is>
       </c>
       <c r="ER46">
+        <v>90</v>
+      </c>
+      <c r="ES46">
         <v>18</v>
       </c>
-      <c r="ES46">
+      <c r="ET46">
         <v>13</v>
       </c>
     </row>
@@ -21111,9 +21251,12 @@
         </is>
       </c>
       <c r="ER47">
+        <v>97</v>
+      </c>
+      <c r="ES47">
         <v>18</v>
       </c>
-      <c r="ES47">
+      <c r="ET47">
         <v>12</v>
       </c>
     </row>
@@ -21544,9 +21687,12 @@
         </is>
       </c>
       <c r="ER48">
+        <v>80</v>
+      </c>
+      <c r="ES48">
         <v>16</v>
       </c>
-      <c r="ES48">
+      <c r="ET48">
         <v>14</v>
       </c>
     </row>
@@ -21977,9 +22123,12 @@
         </is>
       </c>
       <c r="ER49">
+        <v>70</v>
+      </c>
+      <c r="ES49">
         <v>14</v>
       </c>
-      <c r="ES49">
+      <c r="ET49">
         <v>13</v>
       </c>
     </row>
@@ -22405,9 +22554,12 @@
         </is>
       </c>
       <c r="ER50">
+        <v>62</v>
+      </c>
+      <c r="ES50">
         <v>6</v>
       </c>
-      <c r="ES50">
+      <c r="ET50">
         <v>6</v>
       </c>
     </row>
@@ -22833,9 +22985,12 @@
         </is>
       </c>
       <c r="ER51">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="ES51">
+        <v>3</v>
+      </c>
+      <c r="ET51">
         <v>3</v>
       </c>
     </row>
@@ -23261,9 +23416,12 @@
         </is>
       </c>
       <c r="ER52">
+        <v>6</v>
+      </c>
+      <c r="ES52">
         <v>19</v>
       </c>
-      <c r="ES52">
+      <c r="ET52">
         <v>12</v>
       </c>
     </row>
@@ -23689,9 +23847,12 @@
         </is>
       </c>
       <c r="ER53">
+        <v>5</v>
+      </c>
+      <c r="ES53">
         <v>19</v>
       </c>
-      <c r="ES53">
+      <c r="ET53">
         <v>13</v>
       </c>
     </row>
@@ -24146,9 +24307,12 @@
         </is>
       </c>
       <c r="ER54">
+        <v>80</v>
+      </c>
+      <c r="ES54">
         <v>12</v>
       </c>
-      <c r="ES54">
+      <c r="ET54">
         <v>11</v>
       </c>
     </row>
@@ -24603,9 +24767,12 @@
         </is>
       </c>
       <c r="ER55">
+        <v>70</v>
+      </c>
+      <c r="ES55">
         <v>7</v>
       </c>
-      <c r="ES55">
+      <c r="ET55">
         <v>8</v>
       </c>
     </row>
@@ -25048,9 +25215,12 @@
         </is>
       </c>
       <c r="ER56">
+        <v>40</v>
+      </c>
+      <c r="ES56">
         <v>7</v>
       </c>
-      <c r="ES56">
+      <c r="ET56">
         <v>6</v>
       </c>
     </row>
@@ -25491,9 +25661,12 @@
         </is>
       </c>
       <c r="ER57">
+        <v>40</v>
+      </c>
+      <c r="ES57">
         <v>7</v>
       </c>
-      <c r="ES57">
+      <c r="ET57">
         <v>6</v>
       </c>
     </row>
@@ -25919,9 +26092,12 @@
         </is>
       </c>
       <c r="ER58">
+        <v>80</v>
+      </c>
+      <c r="ES58">
         <v>12</v>
       </c>
-      <c r="ES58">
+      <c r="ET58">
         <v>11</v>
       </c>
     </row>
@@ -26347,9 +26523,12 @@
         </is>
       </c>
       <c r="ER59">
+        <v>80</v>
+      </c>
+      <c r="ES59">
         <v>14</v>
       </c>
-      <c r="ES59">
+      <c r="ET59">
         <v>12</v>
       </c>
     </row>
@@ -26775,9 +26954,12 @@
         </is>
       </c>
       <c r="ER60">
+        <v>30</v>
+      </c>
+      <c r="ES60">
         <v>7</v>
       </c>
-      <c r="ES60">
+      <c r="ET60">
         <v>7</v>
       </c>
     </row>
@@ -27124,6 +27306,9 @@
           <t>control</t>
         </is>
       </c>
+      <c r="ER61">
+        <v>60</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -27565,9 +27750,12 @@
         </is>
       </c>
       <c r="ER62">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="ES62">
+        <v>4</v>
+      </c>
+      <c r="ET62">
         <v>3</v>
       </c>
     </row>
@@ -28016,9 +28204,12 @@
         </is>
       </c>
       <c r="ER63">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="ES63">
+        <v>2</v>
+      </c>
+      <c r="ET63">
         <v>2</v>
       </c>
     </row>
@@ -28444,9 +28635,12 @@
         </is>
       </c>
       <c r="ER64">
+        <v>80</v>
+      </c>
+      <c r="ES64">
         <v>6</v>
       </c>
-      <c r="ES64">
+      <c r="ET64">
         <v>5</v>
       </c>
     </row>
@@ -28872,9 +29066,12 @@
         </is>
       </c>
       <c r="ER65">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="ES65">
+        <v>3</v>
+      </c>
+      <c r="ET65">
         <v>2</v>
       </c>
     </row>
@@ -29318,9 +29515,12 @@
         </is>
       </c>
       <c r="ER66">
+        <v>80</v>
+      </c>
+      <c r="ES66">
         <v>10</v>
       </c>
-      <c r="ES66">
+      <c r="ET66">
         <v>12</v>
       </c>
     </row>
@@ -29764,9 +29964,12 @@
         </is>
       </c>
       <c r="ER67">
+        <v>25</v>
+      </c>
+      <c r="ES67">
         <v>8</v>
       </c>
-      <c r="ES67">
+      <c r="ET67">
         <v>10</v>
       </c>
     </row>
@@ -30189,9 +30392,12 @@
         </is>
       </c>
       <c r="ER68">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="ES68">
+        <v>4</v>
+      </c>
+      <c r="ET68">
         <v>5</v>
       </c>
     </row>
@@ -30617,9 +30823,12 @@
         </is>
       </c>
       <c r="ER69">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="ES69">
+        <v>4</v>
+      </c>
+      <c r="ET69">
         <v>5</v>
       </c>
     </row>
@@ -31066,9 +31275,12 @@
         </is>
       </c>
       <c r="ER70">
+        <v>60</v>
+      </c>
+      <c r="ES70">
         <v>10</v>
       </c>
-      <c r="ES70">
+      <c r="ET70">
         <v>10</v>
       </c>
     </row>
@@ -31515,9 +31727,12 @@
         </is>
       </c>
       <c r="ER71">
+        <v>10</v>
+      </c>
+      <c r="ES71">
         <v>6</v>
       </c>
-      <c r="ES71">
+      <c r="ET71">
         <v>6</v>
       </c>
     </row>
@@ -31943,9 +32158,12 @@
         </is>
       </c>
       <c r="ER72">
+        <v>30</v>
+      </c>
+      <c r="ES72">
         <v>17</v>
       </c>
-      <c r="ES72">
+      <c r="ET72">
         <v>12</v>
       </c>
     </row>
@@ -32371,9 +32589,12 @@
         </is>
       </c>
       <c r="ER73">
+        <v>50</v>
+      </c>
+      <c r="ES73">
         <v>14</v>
       </c>
-      <c r="ES73">
+      <c r="ET73">
         <v>10</v>
       </c>
     </row>
@@ -32799,9 +33020,12 @@
         </is>
       </c>
       <c r="ER74">
+        <v>80</v>
+      </c>
+      <c r="ES74">
         <v>14</v>
       </c>
-      <c r="ES74">
+      <c r="ET74">
         <v>12</v>
       </c>
     </row>
@@ -33232,9 +33456,12 @@
         </is>
       </c>
       <c r="ER75">
+        <v>60</v>
+      </c>
+      <c r="ES75">
         <v>9</v>
       </c>
-      <c r="ES75">
+      <c r="ET75">
         <v>8</v>
       </c>
     </row>
@@ -33683,9 +33910,12 @@
         </is>
       </c>
       <c r="ER76">
+        <v>80</v>
+      </c>
+      <c r="ES76">
         <v>13</v>
       </c>
-      <c r="ES76">
+      <c r="ET76">
         <v>13</v>
       </c>
     </row>
@@ -34134,9 +34364,12 @@
         </is>
       </c>
       <c r="ER77">
+        <v>80</v>
+      </c>
+      <c r="ES77">
         <v>14</v>
       </c>
-      <c r="ES77">
+      <c r="ET77">
         <v>12</v>
       </c>
     </row>
@@ -34583,9 +34816,12 @@
         </is>
       </c>
       <c r="ER78">
+        <v>60</v>
+      </c>
+      <c r="ES78">
         <v>9</v>
       </c>
-      <c r="ES78">
+      <c r="ET78">
         <v>8</v>
       </c>
     </row>
@@ -35032,9 +35268,12 @@
         </is>
       </c>
       <c r="ER79">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="ES79">
+        <v>4</v>
+      </c>
+      <c r="ET79">
         <v>3</v>
       </c>
     </row>
@@ -35460,9 +35699,12 @@
         </is>
       </c>
       <c r="ER80">
+        <v>70</v>
+      </c>
+      <c r="ES80">
         <v>12</v>
       </c>
-      <c r="ES80">
+      <c r="ET80">
         <v>9</v>
       </c>
     </row>
@@ -35888,9 +36130,12 @@
         </is>
       </c>
       <c r="ER81">
+        <v>80</v>
+      </c>
+      <c r="ES81">
         <v>11</v>
       </c>
-      <c r="ES81">
+      <c r="ET81">
         <v>8</v>
       </c>
     </row>
@@ -36316,9 +36561,12 @@
         </is>
       </c>
       <c r="ER82">
+        <v>70</v>
+      </c>
+      <c r="ES82">
         <v>11</v>
       </c>
-      <c r="ES82">
+      <c r="ET82">
         <v>10</v>
       </c>
     </row>
@@ -36744,9 +36992,12 @@
         </is>
       </c>
       <c r="ER83">
+        <v>70</v>
+      </c>
+      <c r="ES83">
         <v>12</v>
       </c>
-      <c r="ES83">
+      <c r="ET83">
         <v>12</v>
       </c>
     </row>
@@ -37166,9 +37417,12 @@
         </is>
       </c>
       <c r="ER84">
+        <v>40</v>
+      </c>
+      <c r="ES84">
         <v>8</v>
       </c>
-      <c r="ES84">
+      <c r="ET84">
         <v>6</v>
       </c>
     </row>
@@ -37620,9 +37874,12 @@
         </is>
       </c>
       <c r="ER85">
+        <v>75</v>
+      </c>
+      <c r="ES85">
         <v>13</v>
       </c>
-      <c r="ES85">
+      <c r="ET85">
         <v>10</v>
       </c>
     </row>
@@ -38074,9 +38331,12 @@
         </is>
       </c>
       <c r="ER86">
+        <v>70</v>
+      </c>
+      <c r="ES86">
         <v>8</v>
       </c>
-      <c r="ES86">
+      <c r="ET86">
         <v>7</v>
       </c>
     </row>
@@ -38520,9 +38780,12 @@
         </is>
       </c>
       <c r="ER87">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="ES87">
+        <v>5</v>
+      </c>
+      <c r="ET87">
         <v>4</v>
       </c>
     </row>
@@ -38966,9 +39229,12 @@
         </is>
       </c>
       <c r="ER88">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="ES88">
+        <v>2</v>
+      </c>
+      <c r="ET88">
         <v>2</v>
       </c>
     </row>
@@ -39333,6 +39599,9 @@
           <t>control</t>
         </is>
       </c>
+      <c r="ER89">
+        <v>65</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -39779,9 +40048,12 @@
         </is>
       </c>
       <c r="ER90">
+        <v>70</v>
+      </c>
+      <c r="ES90">
         <v>12</v>
       </c>
-      <c r="ES90">
+      <c r="ET90">
         <v>10</v>
       </c>
     </row>
@@ -40233,9 +40505,12 @@
         </is>
       </c>
       <c r="ER91">
+        <v>80</v>
+      </c>
+      <c r="ES91">
         <v>17</v>
       </c>
-      <c r="ES91">
+      <c r="ET91">
         <v>12</v>
       </c>
     </row>
@@ -40687,9 +40962,12 @@
         </is>
       </c>
       <c r="ER92">
+        <v>30</v>
+      </c>
+      <c r="ES92">
         <v>6</v>
       </c>
-      <c r="ES92">
+      <c r="ET92">
         <v>7</v>
       </c>
     </row>
@@ -41120,9 +41398,12 @@
         </is>
       </c>
       <c r="ER93">
+        <v>70</v>
+      </c>
+      <c r="ES93">
         <v>13</v>
       </c>
-      <c r="ES93">
+      <c r="ET93">
         <v>11</v>
       </c>
     </row>
@@ -41548,9 +41829,12 @@
         </is>
       </c>
       <c r="ER94">
+        <v>80</v>
+      </c>
+      <c r="ES94">
         <v>14</v>
       </c>
-      <c r="ES94">
+      <c r="ET94">
         <v>12</v>
       </c>
     </row>
@@ -41981,9 +42265,12 @@
         </is>
       </c>
       <c r="ER95">
+        <v>80</v>
+      </c>
+      <c r="ES95">
         <v>19</v>
       </c>
-      <c r="ES95">
+      <c r="ET95">
         <v>13</v>
       </c>
     </row>
@@ -42409,9 +42696,12 @@
         </is>
       </c>
       <c r="ER96">
+        <v>70</v>
+      </c>
+      <c r="ES96">
         <v>12</v>
       </c>
-      <c r="ES96">
+      <c r="ET96">
         <v>9</v>
       </c>
     </row>
@@ -42852,9 +43142,12 @@
         </is>
       </c>
       <c r="ER97">
+        <v>80</v>
+      </c>
+      <c r="ES97">
         <v>8</v>
       </c>
-      <c r="ES97">
+      <c r="ET97">
         <v>6</v>
       </c>
     </row>
@@ -43295,9 +43588,12 @@
         </is>
       </c>
       <c r="ER98">
+        <v>40</v>
+      </c>
+      <c r="ES98">
         <v>6</v>
       </c>
-      <c r="ES98">
+      <c r="ET98">
         <v>3</v>
       </c>
     </row>
@@ -43723,9 +44019,12 @@
         </is>
       </c>
       <c r="ER99">
+        <v>80</v>
+      </c>
+      <c r="ES99">
         <v>17</v>
       </c>
-      <c r="ES99">
+      <c r="ET99">
         <v>12</v>
       </c>
     </row>
@@ -44177,9 +44476,12 @@
         </is>
       </c>
       <c r="ER100">
+        <v>60</v>
+      </c>
+      <c r="ES100">
         <v>8</v>
       </c>
-      <c r="ES100">
+      <c r="ET100">
         <v>9</v>
       </c>
     </row>
@@ -44631,9 +44933,12 @@
         </is>
       </c>
       <c r="ER101">
+        <v>90</v>
+      </c>
+      <c r="ES101">
         <v>8</v>
       </c>
-      <c r="ES101">
+      <c r="ET101">
         <v>7</v>
       </c>
     </row>
@@ -45082,9 +45387,12 @@
         </is>
       </c>
       <c r="ER102">
+        <v>67</v>
+      </c>
+      <c r="ES102">
         <v>11</v>
       </c>
-      <c r="ES102">
+      <c r="ET102">
         <v>12</v>
       </c>
     </row>
@@ -45528,9 +45836,12 @@
         </is>
       </c>
       <c r="ER103">
+        <v>60</v>
+      </c>
+      <c r="ES103">
         <v>6</v>
       </c>
-      <c r="ES103">
+      <c r="ET103">
         <v>7</v>
       </c>
     </row>
@@ -45668,6 +45979,9 @@
       <c r="AP104">
         <v>6</v>
       </c>
+      <c r="AQ104">
+        <v>29</v>
+      </c>
       <c r="AR104">
         <v>1</v>
       </c>
@@ -45946,9 +46260,12 @@
         <v>2.9</v>
       </c>
       <c r="ER104">
+        <v>71</v>
+      </c>
+      <c r="ES104">
         <v>19</v>
       </c>
-      <c r="ES104">
+      <c r="ET104">
         <v>14</v>
       </c>
     </row>
@@ -46071,6 +46388,9 @@
       <c r="AP105">
         <v>7</v>
       </c>
+      <c r="AQ105">
+        <v>20</v>
+      </c>
       <c r="AR105">
         <v>1</v>
       </c>
@@ -46333,7 +46653,10 @@
       <c r="EQ105">
         <v>2</v>
       </c>
-      <c r="ES105">
+      <c r="ER105">
+        <v>80</v>
+      </c>
+      <c r="ET105">
         <v>11</v>
       </c>
     </row>
@@ -46647,6 +46970,9 @@
       <c r="AP107">
         <v>1</v>
       </c>
+      <c r="AQ107">
+        <v>90</v>
+      </c>
       <c r="AR107">
         <v>1</v>
       </c>
@@ -46941,9 +47267,12 @@
         <v>9</v>
       </c>
       <c r="ER107">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="ES107">
+        <v>3</v>
+      </c>
+      <c r="ET107">
         <v>3</v>
       </c>
     </row>
@@ -47081,6 +47410,9 @@
       <c r="AP108">
         <v>2</v>
       </c>
+      <c r="AQ108">
+        <v>80</v>
+      </c>
       <c r="AR108">
         <v>1</v>
       </c>
@@ -47380,9 +47712,12 @@
         <v>8</v>
       </c>
       <c r="ER108">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="ES108">
+        <v>3</v>
+      </c>
+      <c r="ET108">
         <v>3</v>
       </c>
     </row>
@@ -47520,6 +47855,9 @@
       <c r="AP109">
         <v>2</v>
       </c>
+      <c r="AQ109">
+        <v>85</v>
+      </c>
       <c r="AR109">
         <v>0</v>
       </c>
@@ -47814,9 +48152,12 @@
         <v>8.5</v>
       </c>
       <c r="ER109">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="ES109">
+        <v>1</v>
+      </c>
+      <c r="ET109">
         <v>1</v>
       </c>
     </row>
@@ -48115,6 +48456,9 @@
       <c r="AP111">
         <v>7</v>
       </c>
+      <c r="AQ111">
+        <v>15</v>
+      </c>
       <c r="AR111">
         <v>1</v>
       </c>
@@ -48409,9 +48753,12 @@
         <v>1.5</v>
       </c>
       <c r="ER111">
+        <v>85</v>
+      </c>
+      <c r="ES111">
         <v>11</v>
       </c>
-      <c r="ES111">
+      <c r="ET111">
         <v>8</v>
       </c>
     </row>
@@ -48549,6 +48896,9 @@
       <c r="AP112">
         <v>7</v>
       </c>
+      <c r="AQ112">
+        <v>25</v>
+      </c>
       <c r="AS112">
         <v>0</v>
       </c>
@@ -48845,9 +49195,12 @@
         <v>2.5</v>
       </c>
       <c r="ER112">
+        <v>75</v>
+      </c>
+      <c r="ES112">
         <v>8</v>
       </c>
-      <c r="ES112">
+      <c r="ET112">
         <v>10</v>
       </c>
     </row>
@@ -49146,6 +49499,9 @@
       <c r="AP114">
         <v>5</v>
       </c>
+      <c r="AQ114">
+        <v>37</v>
+      </c>
       <c r="AR114">
         <v>0</v>
       </c>
@@ -49422,9 +49778,12 @@
         <v>37</v>
       </c>
       <c r="ER114">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="ES114">
+        <v>5</v>
+      </c>
+      <c r="ET114">
         <v>6</v>
       </c>
     </row>
@@ -49556,6 +49915,9 @@
       <c r="AP115">
         <v>5</v>
       </c>
+      <c r="AQ115">
+        <v>37</v>
+      </c>
       <c r="AR115">
         <v>0</v>
       </c>
@@ -49829,9 +50191,12 @@
         <v>37</v>
       </c>
       <c r="ER115">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="ES115">
+        <v>4</v>
+      </c>
+      <c r="ET115">
         <v>6</v>
       </c>
     </row>
@@ -49939,6 +50304,9 @@
       <c r="AG116">
         <v>4264</v>
       </c>
+      <c r="AQ116">
+        <v>70</v>
+      </c>
       <c r="AR116">
         <v>0</v>
       </c>
@@ -50220,7 +50588,10 @@
       <c r="EQ116">
         <v>7</v>
       </c>
-      <c r="ES116">
+      <c r="ER116">
+        <v>30</v>
+      </c>
+      <c r="ET116">
         <v>0</v>
       </c>
     </row>
@@ -50355,6 +50726,9 @@
       <c r="AP117">
         <v>2</v>
       </c>
+      <c r="AQ117">
+        <v>70</v>
+      </c>
       <c r="AR117">
         <v>0</v>
       </c>
@@ -50654,9 +51028,12 @@
         <v>7</v>
       </c>
       <c r="ER117">
+        <v>30</v>
+      </c>
+      <c r="ES117">
         <v>6</v>
       </c>
-      <c r="ES117">
+      <c r="ET117">
         <v>9</v>
       </c>
     </row>
@@ -51003,6 +51380,9 @@
       <c r="AP119">
         <v>7</v>
       </c>
+      <c r="AQ119">
+        <v>18</v>
+      </c>
       <c r="AR119">
         <v>1</v>
       </c>
@@ -51302,9 +51682,12 @@
         <v>1.8</v>
       </c>
       <c r="ER119">
+        <v>82</v>
+      </c>
+      <c r="ES119">
         <v>12</v>
       </c>
-      <c r="ES119">
+      <c r="ET119">
         <v>13</v>
       </c>
     </row>
@@ -51441,6 +51824,9 @@
       </c>
       <c r="AP120">
         <v>7</v>
+      </c>
+      <c r="AQ120">
+        <v>26</v>
       </c>
       <c r="AR120">
         <v>1</v>
@@ -51711,7 +52097,10 @@
       <c r="EQ120">
         <v>2.6</v>
       </c>
-      <c r="ES120">
+      <c r="ER120">
+        <v>74</v>
+      </c>
+      <c r="ET120">
         <v>7</v>
       </c>
     </row>
@@ -51840,6 +52229,9 @@
       <c r="AP121">
         <v>6</v>
       </c>
+      <c r="AQ121">
+        <v>24</v>
+      </c>
       <c r="AR121">
         <v>1</v>
       </c>
@@ -52093,7 +52485,10 @@
       <c r="EQ121">
         <v>2.4</v>
       </c>
-      <c r="ES121">
+      <c r="ER121">
+        <v>76</v>
+      </c>
+      <c r="ET121">
         <v>5</v>
       </c>
     </row>
@@ -52231,6 +52626,9 @@
       <c r="AP122">
         <v>7</v>
       </c>
+      <c r="AQ122">
+        <v>72</v>
+      </c>
       <c r="AR122">
         <v>1</v>
       </c>
@@ -52512,9 +52910,12 @@
         <v>7.2</v>
       </c>
       <c r="ER122">
+        <v>28</v>
+      </c>
+      <c r="ES122">
         <v>10</v>
       </c>
-      <c r="ES122">
+      <c r="ET122">
         <v>8</v>
       </c>
     </row>
@@ -52652,6 +53053,9 @@
       <c r="AP123">
         <v>7</v>
       </c>
+      <c r="AQ123">
+        <v>70</v>
+      </c>
       <c r="AR123">
         <v>0</v>
       </c>
@@ -52925,9 +53329,12 @@
         <v>7</v>
       </c>
       <c r="ER123">
+        <v>30</v>
+      </c>
+      <c r="ES123">
         <v>6</v>
       </c>
-      <c r="ES123">
+      <c r="ET123">
         <v>7</v>
       </c>
     </row>
@@ -53065,6 +53472,9 @@
       <c r="AP124">
         <v>3</v>
       </c>
+      <c r="AQ124">
+        <v>70</v>
+      </c>
       <c r="AR124">
         <v>1</v>
       </c>
@@ -53364,9 +53774,12 @@
         <v>7</v>
       </c>
       <c r="ER124">
+        <v>30</v>
+      </c>
+      <c r="ES124">
         <v>8</v>
       </c>
-      <c r="ES124">
+      <c r="ET124">
         <v>8</v>
       </c>
     </row>
@@ -53504,6 +53917,9 @@
       <c r="AP125">
         <v>3</v>
       </c>
+      <c r="AQ125">
+        <v>56</v>
+      </c>
       <c r="AR125">
         <v>2</v>
       </c>
@@ -53806,9 +54222,12 @@
         <v>5.6</v>
       </c>
       <c r="ER125">
+        <v>44</v>
+      </c>
+      <c r="ES125">
         <v>8</v>
       </c>
-      <c r="ES125">
+      <c r="ET125">
         <v>9</v>
       </c>
     </row>
@@ -53946,6 +54365,9 @@
       <c r="AP126">
         <v>2</v>
       </c>
+      <c r="AQ126">
+        <v>86</v>
+      </c>
       <c r="AR126">
         <v>1</v>
       </c>
@@ -54240,9 +54662,12 @@
         <v>8.6</v>
       </c>
       <c r="ER126">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="ES126">
+        <v>3</v>
+      </c>
+      <c r="ET126">
         <v>4</v>
       </c>
     </row>
@@ -54380,6 +54805,9 @@
       <c r="AP127">
         <v>2</v>
       </c>
+      <c r="AQ127">
+        <v>40</v>
+      </c>
       <c r="AR127">
         <v>1</v>
       </c>
@@ -54671,9 +55099,12 @@
         <v>4</v>
       </c>
       <c r="ER127">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="ES127">
+        <v>3</v>
+      </c>
+      <c r="ET127">
         <v>3</v>
       </c>
     </row>
@@ -54811,6 +55242,9 @@
       <c r="AP128">
         <v>4</v>
       </c>
+      <c r="AQ128">
+        <v>60</v>
+      </c>
       <c r="AR128">
         <v>1</v>
       </c>
@@ -55102,9 +55536,12 @@
         <v>6</v>
       </c>
       <c r="ER128">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="ES128">
+        <v>4</v>
+      </c>
+      <c r="ET128">
         <v>4</v>
       </c>
     </row>
@@ -55212,6 +55649,9 @@
       <c r="AP129">
         <v>6</v>
       </c>
+      <c r="AQ129">
+        <v>76</v>
+      </c>
       <c r="DC129">
         <v>1517</v>
       </c>
@@ -55318,6 +55758,9 @@
       </c>
       <c r="EQ129">
         <v>7.6</v>
+      </c>
+      <c r="ER129">
+        <v>24</v>
       </c>
     </row>
     <row r="130">
@@ -55454,6 +55897,9 @@
       <c r="AP130">
         <v>7</v>
       </c>
+      <c r="AQ130">
+        <v>80</v>
+      </c>
       <c r="AR130">
         <v>1</v>
       </c>
@@ -55753,9 +56199,12 @@
         <v>8</v>
       </c>
       <c r="ER130">
+        <v>20</v>
+      </c>
+      <c r="ES130">
         <v>16</v>
       </c>
-      <c r="ES130">
+      <c r="ET130">
         <v>12</v>
       </c>
     </row>
@@ -55893,6 +56342,9 @@
       <c r="AP131">
         <v>4</v>
       </c>
+      <c r="AQ131">
+        <v>50</v>
+      </c>
       <c r="AR131">
         <v>2</v>
       </c>
@@ -56187,9 +56639,12 @@
         <v>5</v>
       </c>
       <c r="ER131">
+        <v>50</v>
+      </c>
+      <c r="ES131">
         <v>11</v>
       </c>
-      <c r="ES131">
+      <c r="ET131">
         <v>11</v>
       </c>
     </row>
@@ -56327,6 +56782,9 @@
       <c r="AP132">
         <v>4</v>
       </c>
+      <c r="AQ132">
+        <v>50</v>
+      </c>
       <c r="AR132">
         <v>1</v>
       </c>
@@ -56629,9 +57087,12 @@
         <v>5</v>
       </c>
       <c r="ER132">
+        <v>50</v>
+      </c>
+      <c r="ES132">
         <v>7</v>
       </c>
-      <c r="ES132">
+      <c r="ET132">
         <v>8</v>
       </c>
     </row>
@@ -56769,6 +57230,9 @@
       <c r="AP133">
         <v>3</v>
       </c>
+      <c r="AQ133">
+        <v>90</v>
+      </c>
       <c r="AR133">
         <v>1</v>
       </c>
@@ -57071,9 +57535,12 @@
         <v>9</v>
       </c>
       <c r="ER133">
+        <v>10</v>
+      </c>
+      <c r="ES133">
         <v>9</v>
       </c>
-      <c r="ES133">
+      <c r="ET133">
         <v>10</v>
       </c>
     </row>
@@ -57211,6 +57678,9 @@
       <c r="AP134">
         <v>5</v>
       </c>
+      <c r="AQ134">
+        <v>20</v>
+      </c>
       <c r="AS134">
         <v>0</v>
       </c>
@@ -57501,9 +57971,12 @@
         <v>2</v>
       </c>
       <c r="ER134">
+        <v>80</v>
+      </c>
+      <c r="ES134">
         <v>8</v>
       </c>
-      <c r="ES134">
+      <c r="ET134">
         <v>8</v>
       </c>
     </row>
@@ -57641,6 +58114,9 @@
       <c r="AP135">
         <v>7</v>
       </c>
+      <c r="AQ135">
+        <v>30</v>
+      </c>
       <c r="AR135">
         <v>2</v>
       </c>
@@ -57917,9 +58393,12 @@
         <v>3</v>
       </c>
       <c r="ER135">
+        <v>70</v>
+      </c>
+      <c r="ES135">
         <v>11</v>
       </c>
-      <c r="ES135">
+      <c r="ET135">
         <v>11</v>
       </c>
     </row>
@@ -58057,6 +58536,9 @@
       <c r="AP136">
         <v>7</v>
       </c>
+      <c r="AQ136">
+        <v>70</v>
+      </c>
       <c r="AR136">
         <v>1</v>
       </c>
@@ -58330,9 +58812,12 @@
         <v>7</v>
       </c>
       <c r="ER136">
+        <v>30</v>
+      </c>
+      <c r="ES136">
         <v>18</v>
       </c>
-      <c r="ES136">
+      <c r="ET136">
         <v>11</v>
       </c>
     </row>
@@ -58470,6 +58955,9 @@
       <c r="AP137">
         <v>7</v>
       </c>
+      <c r="AQ137">
+        <v>20</v>
+      </c>
       <c r="AR137">
         <v>2</v>
       </c>
@@ -58746,9 +59234,12 @@
         <v>2</v>
       </c>
       <c r="ER137">
+        <v>80</v>
+      </c>
+      <c r="ES137">
         <v>12</v>
       </c>
-      <c r="ES137">
+      <c r="ET137">
         <v>12</v>
       </c>
     </row>
